--- a/data/trans_orig/cron_prev_index-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la prevalencia</t>
+          <t>Índice de cronicidad física en base a la prevalencia (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,48</t>
+          <t>0,31; 0,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,6</t>
+          <t>0,38; 0,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,78</t>
+          <t>0,55; 0,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,59</t>
+          <t>0,4; 0,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,74</t>
+          <t>0,53; 0,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,73</t>
+          <t>0,45; 0,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,72</t>
+          <t>0,55; 0,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,52</t>
+          <t>0,37; 0,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,63</t>
+          <t>0,47; 0,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,62</t>
+          <t>0,46; 0,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,72</t>
+          <t>0,58; 0,71</t>
         </is>
       </c>
     </row>
@@ -856,37 +856,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,47</t>
+          <t>0,34; 0,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,65</t>
+          <t>0,45; 0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,59</t>
+          <t>0,43; 0,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,72</t>
+          <t>0,53; 0,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,8</t>
+          <t>0,62; 0,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,82</t>
+          <t>0,63; 0,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,83</t>
+          <t>0,65; 0,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,61</t>
+          <t>0,5; 0,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,7</t>
+          <t>0,56; 0,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,49</t>
+          <t>0,33; 0,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,71</t>
+          <t>0,49; 0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,59</t>
+          <t>0,41; 0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,84</t>
+          <t>0,62; 0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,76</t>
+          <t>0,56; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,67</t>
+          <t>0,46; 0,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,96</t>
+          <t>0,76; 0,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,77</t>
+          <t>0,62; 0,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,88</t>
+          <t>0,71; 0,87</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,53</t>
+          <t>0,36; 0,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,83</t>
+          <t>0,57; 0,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,9</t>
+          <t>0,66; 0,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,87</t>
+          <t>0,66; 0,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,93</t>
+          <t>0,61; 0,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,59</t>
+          <t>0,47; 0,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,74</t>
+          <t>0,59; 0,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,77</t>
+          <t>0,61; 0,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,84</t>
+          <t>0,65; 0,85</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1276,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,59</t>
+          <t>0,36; 0,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,8</t>
+          <t>0,48; 0,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,58</t>
+          <t>0,36; 0,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,22 +1296,22 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,89</t>
+          <t>0,56; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,15</t>
+          <t>0,81; 1,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,85</t>
+          <t>0,57; 0,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,09</t>
+          <t>0,48; 1,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,91</t>
+          <t>0,69; 0,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,68</t>
+          <t>0,51; 0,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,95</t>
+          <t>0,57; 0,95</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,53</t>
+          <t>0,35; 0,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,78</t>
+          <t>0,54; 0,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,98</t>
+          <t>0,72; 0,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,79</t>
+          <t>0,55; 0,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,1</t>
+          <t>0,88; 1,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,87</t>
+          <t>0,69; 0,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1556,47 +1556,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,51</t>
+          <t>0,37; 0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,64</t>
+          <t>0,49; 0,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,6</t>
+          <t>0,45; 0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,78</t>
+          <t>0,62; 0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,69</t>
+          <t>0,53; 0,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,78</t>
+          <t>0,63; 0,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,65</t>
+          <t>0,49; 0,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,1</t>
+          <t>0,84; 2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,58</t>
+          <t>0,47; 0,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,6</t>
+          <t>0,49; 0,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,86</t>
+          <t>0,76; 1,77</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,63</t>
+          <t>0,5; 0,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1716,27 +1716,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,79</t>
+          <t>0,62; 0,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,63</t>
+          <t>0,49; 0,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,76</t>
+          <t>0,61; 0,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,81</t>
+          <t>0,65; 0,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,69</t>
+          <t>0,58; 0,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,67</t>
+          <t>0,56; 0,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,65</t>
+          <t>0,34; 0,66</t>
         </is>
       </c>
     </row>
@@ -1851,32 +1851,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,69</t>
+          <t>0,49; 0,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>0,62; 0,68</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,67; 0,74</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>0,62; 0,69</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 0,75</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 0,69</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,3</t>
+          <t>0,78; 1,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,57</t>
+          <t>0,53; 0,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,0</t>
+          <t>0,69; 0,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_prev_index-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0,54</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
         </is>
       </c>
     </row>
@@ -721,37 +721,37 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,59</t>
+          <t>0,39; 0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,61</t>
+          <t>0,4; 0,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,78</t>
+          <t>0,55; 0,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,6</t>
+          <t>0,39; 0,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,76</t>
+          <t>0,52; 0,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,7</t>
+          <t>0,46; 0,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,73</t>
+          <t>0,53; 0,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,63</t>
+          <t>0,48; 0,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,63</t>
+          <t>0,46; 0,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,71</t>
+          <t>0,57; 0,7</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,47</t>
+          <t>0,33; 0,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,64</t>
+          <t>0,44; 0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -881,17 +881,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,83</t>
+          <t>0,63; 0,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,83</t>
+          <t>0,64; 0,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,74</t>
+          <t>0,58; 0,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,69</t>
+          <t>0,56; 0,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,7</t>
+          <t>0,58; 0,69</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,5</t>
+          <t>0,33; 0,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,72</t>
+          <t>0,5; 0,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,59</t>
+          <t>0,42; 0,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,76</t>
+          <t>0,55; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,91</t>
+          <t>0,67; 0,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 0,97</t>
+          <t>0,73; 0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,78</t>
+          <t>0,61; 0,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>0,69</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,52</t>
+          <t>0,36; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,7</t>
+          <t>0,52; 0,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,82</t>
+          <t>0,54; 0,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,71</t>
+          <t>0,53; 0,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,9</t>
+          <t>0,67; 0,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,88</t>
+          <t>0,67; 0,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,91</t>
+          <t>0,71; 0,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,58</t>
+          <t>0,47; 0,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,75</t>
+          <t>0,59; 0,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,76</t>
+          <t>0,62; 0,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,85</t>
+          <t>0,66; 0,81</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,36; 0,6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,48; 0,78</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0,36; 0,58</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 0,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 0,58</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,9</t>
+          <t>0,59; 0,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,9</t>
+          <t>0,58; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,18</t>
+          <t>0,81; 1,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,87</t>
+          <t>0,56; 0,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,09</t>
+          <t>0,89; 1,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,7</t>
+          <t>0,49; 0,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,94</t>
+          <t>0,68; 0,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,7</t>
+          <t>0,5; 0,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,95</t>
+          <t>0,78; 0,95</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,52</t>
+          <t>0,36; 0,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,83</t>
+          <t>0,59; 0,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,1</t>
+          <t>0,85; 1,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,76</t>
+          <t>0,54; 0,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,99</t>
+          <t>0,73; 0,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,79</t>
+          <t>0,54; 0,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,1</t>
+          <t>0,87; 1,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,87</t>
+          <t>0,68; 0,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,66</t>
+          <t>0,49; 0,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,06</t>
+          <t>0,89; 1,05</t>
         </is>
       </c>
     </row>
@@ -1503,19 +1503,19 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,57</t>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -1561,37 +1561,37 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,64</t>
+          <t>0,49; 0,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,6</t>
+          <t>0,45; 0,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,79</t>
+          <t>0,65; 0,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,7</t>
+          <t>0,53; 0,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,79</t>
+          <t>0,62; 0,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,66</t>
+          <t>0,49; 0,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,2</t>
+          <t>0,81; 0,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,61</t>
+          <t>0,49; 0,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,77</t>
+          <t>0,75; 0,86</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,5</t>
+          <t>0,38; 0,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,27 +1711,27 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,57</t>
+          <t>0,47; 0,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,78</t>
+          <t>0,63; 0,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,64</t>
+          <t>0,49; 0,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,75</t>
+          <t>0,6; 0,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,8</t>
+          <t>0,64; 0,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,55</t>
+          <t>0,45; 0,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,66</t>
+          <t>0,58; 0,67</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,69</t>
+          <t>0,63; 0,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,68</t>
+          <t>0,62; 0,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,29</t>
+          <t>0,76; 0,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,61</t>
+          <t>0,57; 0,61</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,98</t>
+          <t>0,71; 0,75</t>
         </is>
       </c>
     </row>
